--- a/academics/DB1/RMF/BIV-300_RMF.xlsx
+++ b/academics/DB1/RMF/BIV-300_RMF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\oicampo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6D8CD6-0CE6-480A-9CD9-8AA23A98DB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E13DC9-5344-49DB-B3C4-4744D4E6F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_RMP" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="310">
   <si>
     <t>Risk Management Plan (RMP)</t>
   </si>
@@ -211,6 +211,12 @@
     <t>ACCEPTABILITY MATRIX</t>
   </si>
   <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
     <t>ALARP</t>
   </si>
   <si>
@@ -403,9 +409,6 @@
     <t>Effect_Patient</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>P1_method</t>
   </si>
   <si>
@@ -974,12 +977,6 @@
   </si>
   <si>
     <t>⚠️  INSTRUCCIONES: 1) Completa 01_PHA → 2) Analiza en 02/03 FMEA → 3) Dashboard se actualiza automáticamente → 4) Columnas en AMARILLO son automáticas, NO editar</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           P</t>
   </si>
 </sst>
 </file>
@@ -989,7 +986,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1085,14 +1082,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1153,7 +1142,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1211,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1277,9 +1266,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1295,25 +1300,6 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1334,9 +1320,9 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="10"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1358,7 +1344,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.5077160493827158E-2"/>
+          <c:y val="3.0683403068340307E-2"/>
+          <c:w val="0.74853904320987652"/>
+          <c:h val="0.87168758716875872"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1368,11 +1364,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$B$12</c:f>
+              <c:f>Dashboard!$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Inicial</c:v>
+                  <c:v>❌ INACEPTABLE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1383,44 +1379,201 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$13:$A$16</c:f>
+              <c:f>Dashboard!$B$12:$C$12</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>❌ INACEPTABLE</c:v>
+                  <c:v>Inicial</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>ALARP</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>✅ ACEPTABLE</c:v>
+                  <c:v>Residual</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$13:$B$16</c:f>
+              <c:f>Dashboard!$B$13:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5A87-4B44-9BAB-0097C0FF2598}"/>
+              <c16:uniqueId val="{00000000-5215-4198-A373-8228DDB2BB93}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ALARP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$B$12:$C$12</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Inicial</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Residual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$14:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5215-4198-A373-8228DDB2BB93}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>✅ ACEPTABLE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$B$12:$C$12</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Inicial</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Residual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$15:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5215-4198-A373-8228DDB2BB93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1454,11 +1607,19 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="es-CO"/>
-                  <a:t>Estado</a:t>
+                  <a:t>INICIAL                                                                     RESIDUAL</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.18219182098765432"/>
+              <c:y val="0.92740596755949445"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1532,7 +1693,7 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6480000" cy="4320000"/>
+    <xdr:ext cx="6480000" cy="4552950"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -1845,19 +2006,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="30"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1894,7 +2054,7 @@
       </c>
       <c r="B7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1906,10 +2066,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="37"/>
+      <c r="B10" s="30"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -1922,7 +2082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -1933,7 +2093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
@@ -1944,7 +2104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
@@ -1955,7 +2115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1978,10 +2138,10 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="37"/>
+      <c r="B19" s="30"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1997,7 +2157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>33</v>
       </c>
@@ -2011,7 +2171,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
@@ -2025,7 +2185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>41</v>
       </c>
@@ -2039,7 +2199,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>45</v>
       </c>
@@ -2053,7 +2213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
@@ -2068,36 +2228,36 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="C29" s="5" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="29">
+      <c r="B30" s="39"/>
+      <c r="C30" s="38">
         <v>1</v>
       </c>
       <c r="D30" s="5">
@@ -2114,124 +2274,124 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="43">
         <v>5</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>54</v>
+      <c r="C31" s="40" t="s">
+        <v>56</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="B32" s="43">
+        <v>4</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="B33" s="43">
+        <v>3</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="42" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B32" s="33">
-        <v>4</v>
-      </c>
-      <c r="C32" s="31" t="s">
+      <c r="B34" s="43">
+        <v>2</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="10" t="s">
+      <c r="G34" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B33" s="33">
-        <v>3</v>
-      </c>
-      <c r="C33" s="31" t="s">
+      <c r="B35" s="44">
+        <v>1</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B34" s="33">
-        <v>2</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B35" s="34">
-        <v>1</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -2241,38 +2401,38 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+    <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B4" s="27">
         <f>COUNTA('01_PHA'!A4:A18)</f>
@@ -2281,7 +2441,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B5" s="27">
         <f>COUNTA('04_Risk_Eval'!A4:A20)</f>
@@ -2290,7 +2450,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B6" s="27">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"❌*")</f>
@@ -2299,7 +2459,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B7" s="27">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"ALARP*")</f>
@@ -2308,7 +2468,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B8" s="27">
         <f>COUNTIF('04_Risk_Eval'!H4:H20,"❌*")</f>
@@ -2317,7 +2477,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B9" s="27">
         <f>COUNTIF('04_Risk_Eval'!H4:H20,"✅*")</f>
@@ -2325,30 +2485,30 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
+      <c r="A11" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B13" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"❌*")</f>
@@ -2361,7 +2521,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"ALARP*")</f>
@@ -2374,7 +2534,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B15" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"✅*")</f>
@@ -2385,17 +2545,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
-        <v>308</v>
-      </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="N32" s="45"/>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2412,7 +2571,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2421,285 +2580,285 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2713,81 +2872,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="19" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
+    <row r="1" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-    </row>
-    <row r="3" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+    </row>
+    <row r="3" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>37</v>
@@ -2796,57 +2955,57 @@
         <v>41</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E4" s="17">
         <v>5</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G4" s="19">
         <v>2.9999999999999998E-14</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I4" s="18">
         <v>0.02</v>
@@ -2866,9 +3025,6 @@
         <f t="shared" ref="M4:M13" si="2">INDEX(MatrizAceptabilidad,MATCH(L4,NivelesP,0),MATCH(E4,NivelesS,0))</f>
         <v>ALARP</v>
       </c>
-      <c r="N4" s="28"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
       <c r="Q4" s="20">
         <f t="shared" ref="Q4:Q13" si="3">G4*O4*P4</f>
         <v>0</v>
@@ -2884,28 +3040,28 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E5" s="17">
         <v>4</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" s="19">
         <v>2.7599999999999999E-3</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I5" s="18">
         <v>6.0000000000000001E-3</v>
@@ -2925,9 +3081,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="N5" s="28"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
       <c r="Q5" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2943,28 +3096,28 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6" s="17">
         <v>5</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G6" s="19">
         <v>0.15</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I6" s="18">
         <v>1.7999999999999999E-2</v>
@@ -2984,9 +3137,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="N6" s="28"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
       <c r="Q6" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3002,28 +3152,28 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E7" s="17">
         <v>5</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" s="19">
         <v>1E-10</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I7" s="18">
         <v>0.03</v>
@@ -3043,9 +3193,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
       <c r="Q7" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3061,28 +3208,28 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E8" s="17">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G8" s="19">
         <v>5.5000000000000003E-4</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I8" s="18">
         <v>0.01</v>
@@ -3102,9 +3249,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
       <c r="Q8" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3120,28 +3264,28 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9" s="17">
         <v>5</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G9" s="19">
         <v>1E-3</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I9" s="18">
         <v>0.05</v>
@@ -3161,9 +3305,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="N9" s="28"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
       <c r="Q9" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3179,28 +3320,28 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E10" s="17">
         <v>4</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="19">
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I10" s="18">
         <v>0.1</v>
@@ -3220,9 +3361,6 @@
         <f t="shared" si="2"/>
         <v>✅</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
       <c r="Q10" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3238,28 +3376,28 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11" s="17">
         <v>5</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G11" s="19">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I11" s="18">
         <v>8.0000000000000002E-3</v>
@@ -3279,9 +3417,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
       <c r="Q11" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3297,28 +3432,28 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="17">
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G12" s="19">
         <v>0.1</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I12" s="18">
         <v>0.05</v>
@@ -3338,9 +3473,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
       <c r="Q12" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3356,28 +3488,28 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E13" s="17">
         <v>3</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G13" s="19">
         <v>0.08</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I13" s="18">
         <v>0.02</v>
@@ -3397,9 +3529,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="N13" s="28"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
       <c r="Q13" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3425,76 +3554,76 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
+    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-    </row>
-    <row r="3" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+    </row>
+    <row r="3" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>37</v>
@@ -3503,54 +3632,54 @@
         <v>41</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D4" s="17">
         <v>5</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F4" s="18">
         <v>0.2</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H4" s="18">
         <v>1.2E-2</v>
@@ -3570,9 +3699,6 @@
         <f t="shared" ref="L4:L10" si="2">INDEX(MatrizAceptabilidad,MATCH(K4,NivelesP,0),MATCH(D4,NivelesS,0))</f>
         <v>❌</v>
       </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
       <c r="P4" s="20">
         <f t="shared" ref="P4:P10" si="3">F4*N4*O4</f>
         <v>0</v>
@@ -3588,25 +3714,25 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D5" s="17">
         <v>4</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F5" s="18">
         <v>0.05</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H5" s="18">
         <v>0.01</v>
@@ -3626,9 +3752,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
       <c r="P5" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3644,25 +3767,25 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D6" s="17">
         <v>4</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F6" s="18">
         <v>0.15</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H6" s="18">
         <v>0.02</v>
@@ -3682,9 +3805,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
       <c r="P6" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3700,25 +3820,25 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7" s="17">
         <v>4</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F7" s="18">
         <v>0.1</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="18">
         <v>0.03</v>
@@ -3738,9 +3858,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
       <c r="P7" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3756,25 +3873,25 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D8" s="17">
         <v>3</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F8" s="18">
         <v>0.08</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H8" s="18">
         <v>1.4999999999999999E-2</v>
@@ -3794,9 +3911,6 @@
         <f t="shared" si="2"/>
         <v>ALARP</v>
       </c>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
       <c r="P8" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3812,25 +3926,25 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D9" s="17">
         <v>5</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F9" s="18">
         <v>0.12</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H9" s="18">
         <v>0.02</v>
@@ -3850,9 +3964,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
       <c r="P9" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3868,25 +3979,25 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" s="17">
         <v>4</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F10" s="18">
         <v>0.25</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H10" s="18">
         <v>8.0000000000000002E-3</v>
@@ -3906,9 +4017,6 @@
         <f t="shared" si="2"/>
         <v>❌</v>
       </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
       <c r="P10" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3934,64 +4042,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="A2" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B4" s="21" t="str">
         <f>VLOOKUP(A4,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4024,7 +4134,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="21" t="str">
         <f>VLOOKUP(A5,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4057,7 +4167,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="21" t="str">
         <f>VLOOKUP(A6,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4090,7 +4200,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="21" t="str">
         <f>VLOOKUP(A7,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4123,7 +4233,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8" s="21" t="str">
         <f>VLOOKUP(A8,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4156,7 +4266,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B9" s="21" t="str">
         <f>VLOOKUP(A9,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4189,7 +4299,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="21" t="str">
         <f>VLOOKUP(A10,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4222,7 +4332,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B11" s="21" t="str">
         <f>VLOOKUP(A11,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4255,7 +4365,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" s="21" t="str">
         <f>VLOOKUP(A12,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4288,7 +4398,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="21" t="str">
         <f>VLOOKUP(A13,'02_dFMEA'!$A:$S,2,FALSE)</f>
@@ -4321,7 +4431,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" s="21" t="str">
         <f>VLOOKUP(A14,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4354,7 +4464,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B15" s="21" t="str">
         <f>VLOOKUP(A15,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4387,7 +4497,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B16" s="21" t="str">
         <f>VLOOKUP(A16,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4420,7 +4530,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="21" t="str">
         <f>VLOOKUP(A17,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4453,7 +4563,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" s="21" t="str">
         <f>VLOOKUP(A18,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4486,7 +4596,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="21" t="str">
         <f>VLOOKUP(A19,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4519,7 +4629,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B20" s="21" t="str">
         <f>VLOOKUP(A20,'03_uFMEA'!$A:$R,2,FALSE)</f>
@@ -4562,539 +4672,539 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" s="21">
-        <f>VLOOKUP(B4,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B4,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B4,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>5</v>
       </c>
       <c r="D4" s="21">
-        <f>VLOOKUP(B4,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B4,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B4,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E4" s="21" t="str">
-        <f>VLOOKUP(B4,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B4,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B4,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I4" s="21">
-        <f>VLOOKUP(B4,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B4,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B4,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J4" s="21" t="str">
-        <f>VLOOKUP(B4,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B4,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B4,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="21">
-        <f>VLOOKUP(B5,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B5,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B5,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>4</v>
       </c>
       <c r="D5" s="21">
-        <f>VLOOKUP(B5,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B5,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B5,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E5" s="21" t="str">
-        <f>VLOOKUP(B5,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B5,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B5,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I5" s="21">
-        <f>VLOOKUP(B5,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B5,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B5,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J5" s="21" t="str">
-        <f>VLOOKUP(B5,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B5,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B5,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="21">
+        <f>IFERROR(VLOOKUP(B6,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B6,'03_uFMEA'!$A:$R,4,FALSE))</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="21">
+        <f>IFERROR(VLOOKUP(B6,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B6,'03_uFMEA'!$A:$R,11,FALSE))</f>
+        <v>3</v>
+      </c>
+      <c r="E6" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B6,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B6,'03_uFMEA'!$A:$R,12,FALSE))</f>
+        <v>❌</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="21">
+        <f>IFERROR(VLOOKUP(B6,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B6,'03_uFMEA'!$A:$R,17,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B6,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B6,'03_uFMEA'!$A:$R,18,FALSE))</f>
+        <v>ALARP</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>210</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="21">
-        <f>VLOOKUP(B6,'02_dFMEA'!$A:$S,5,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="D6" s="21">
-        <f>VLOOKUP(B6,'02_dFMEA'!$A:$S,12,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E6" s="21" t="str">
-        <f>VLOOKUP(B6,'02_dFMEA'!$A:$S,13,FALSE)</f>
-        <v>❌</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" s="21">
-        <f>VLOOKUP(B6,'02_dFMEA'!$A:$S,18,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="21" t="str">
-        <f>VLOOKUP(B6,'02_dFMEA'!$A:$S,19,FALSE)</f>
-        <v>ALARP</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" s="21">
-        <f>VLOOKUP(B7,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B7,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B7,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>5</v>
       </c>
       <c r="D7" s="21">
-        <f>VLOOKUP(B7,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B7,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B7,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E7" s="21" t="str">
-        <f>VLOOKUP(B7,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B7,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B7,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I7" s="21">
-        <f>VLOOKUP(B7,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B7,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B7,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J7" s="21" t="str">
-        <f>VLOOKUP(B7,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B7,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B7,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" s="21">
-        <f>VLOOKUP(B8,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B8,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B8,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>4</v>
       </c>
       <c r="D8" s="21">
-        <f>VLOOKUP(B8,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B8,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B8,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E8" s="21" t="str">
-        <f>VLOOKUP(B8,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B8,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B8,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I8" s="21">
-        <f>VLOOKUP(B8,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B8,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B8,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J8" s="21" t="str">
-        <f>VLOOKUP(B8,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B8,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B8,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" s="21">
-        <f>VLOOKUP(B9,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B9,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B9,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>5</v>
       </c>
       <c r="D9" s="21">
-        <f>VLOOKUP(B9,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B9,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B9,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>3</v>
       </c>
       <c r="E9" s="21" t="str">
-        <f>VLOOKUP(B9,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B9,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B9,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>❌</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I9" s="21">
-        <f>VLOOKUP(B9,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B9,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B9,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J9" s="21" t="str">
-        <f>VLOOKUP(B9,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B9,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B9,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C10" s="21">
-        <f>VLOOKUP(B10,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B10,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B10,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>4</v>
       </c>
       <c r="D10" s="21">
-        <f>VLOOKUP(B10,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B10,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B10,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>1</v>
       </c>
       <c r="E10" s="21" t="str">
-        <f>VLOOKUP(B10,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B10,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B10,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I10" s="21">
-        <f>VLOOKUP(B10,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B10,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B10,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J10" s="21" t="str">
-        <f>VLOOKUP(B10,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B10,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B10,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" s="21">
-        <f>VLOOKUP(B11,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B11,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B11,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>5</v>
       </c>
       <c r="D11" s="21">
-        <f>VLOOKUP(B11,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B11,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B11,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>2</v>
       </c>
       <c r="E11" s="21" t="str">
-        <f>VLOOKUP(B11,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B11,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B11,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I11" s="21">
-        <f>VLOOKUP(B11,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B11,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B11,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J11" s="21" t="str">
-        <f>VLOOKUP(B11,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B11,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B11,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="21">
-        <f>VLOOKUP(B12,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B12,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B12,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>3</v>
       </c>
       <c r="D12" s="21">
-        <f>VLOOKUP(B12,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B12,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B12,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>5</v>
       </c>
       <c r="E12" s="21" t="str">
-        <f>VLOOKUP(B12,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B12,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B12,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>❌</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I12" s="21">
-        <f>VLOOKUP(B12,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B12,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B12,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J12" s="21" t="str">
-        <f>VLOOKUP(B12,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B12,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B12,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C13" s="21">
-        <f>VLOOKUP(B13,'02_dFMEA'!$A:$S,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B13,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B13,'03_uFMEA'!$A:$R,4,FALSE))</f>
         <v>3</v>
       </c>
       <c r="D13" s="21">
-        <f>VLOOKUP(B13,'02_dFMEA'!$A:$S,12,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B13,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B13,'03_uFMEA'!$A:$R,11,FALSE))</f>
         <v>4</v>
       </c>
       <c r="E13" s="21" t="str">
-        <f>VLOOKUP(B13,'02_dFMEA'!$A:$S,13,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B13,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B13,'03_uFMEA'!$A:$R,12,FALSE))</f>
         <v>ALARP</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I13" s="21">
-        <f>VLOOKUP(B13,'02_dFMEA'!$A:$S,18,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B13,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B13,'03_uFMEA'!$A:$R,17,FALSE))</f>
         <v>1</v>
       </c>
       <c r="J13" s="21" t="str">
-        <f>VLOOKUP(B13,'02_dFMEA'!$A:$S,19,FALSE)</f>
+        <f>IFERROR(VLOOKUP(B13,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B13,'03_uFMEA'!$A:$R,18,FALSE))</f>
         <v>✅</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="21" t="e">
-        <f>VLOOKUP(B14,'02_dFMEA'!$A:$S,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D14" s="21" t="e">
-        <f>VLOOKUP(B14,'02_dFMEA'!$A:$S,12,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E14" s="21" t="e">
-        <f>VLOOKUP(B14,'02_dFMEA'!$A:$S,13,FALSE)</f>
-        <v>#N/A</v>
+        <v>69</v>
+      </c>
+      <c r="C14" s="21">
+        <f>IFERROR(VLOOKUP(B14,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B14,'03_uFMEA'!$A:$R,4,FALSE))</f>
+        <v>5</v>
+      </c>
+      <c r="D14" s="21">
+        <f>IFERROR(VLOOKUP(B14,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B14,'03_uFMEA'!$A:$R,11,FALSE))</f>
+        <v>5</v>
+      </c>
+      <c r="E14" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B14,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B14,'03_uFMEA'!$A:$R,12,FALSE))</f>
+        <v>❌</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="I14" s="21" t="e">
-        <f>VLOOKUP(B14,'02_dFMEA'!$A:$S,18,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J14" s="21" t="e">
-        <f>VLOOKUP(B14,'02_dFMEA'!$A:$S,19,FALSE)</f>
-        <v>#N/A</v>
+        <v>238</v>
+      </c>
+      <c r="I14" s="21">
+        <f>IFERROR(VLOOKUP(B14,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B14,'03_uFMEA'!$A:$R,17,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B14,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B14,'03_uFMEA'!$A:$R,18,FALSE))</f>
+        <v>ALARP</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="21" t="e">
-        <f>VLOOKUP(B15,'02_dFMEA'!$A:$S,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D15" s="21" t="e">
-        <f>VLOOKUP(B15,'02_dFMEA'!$A:$S,12,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E15" s="21" t="e">
-        <f>VLOOKUP(B15,'02_dFMEA'!$A:$S,13,FALSE)</f>
-        <v>#N/A</v>
+        <v>88</v>
+      </c>
+      <c r="C15" s="21">
+        <f>IFERROR(VLOOKUP(B15,'02_dFMEA'!$A:$S,5,FALSE),VLOOKUP(B15,'03_uFMEA'!$A:$R,4,FALSE))</f>
+        <v>4</v>
+      </c>
+      <c r="D15" s="21">
+        <f>IFERROR(VLOOKUP(B15,'02_dFMEA'!$A:$S,12,FALSE),VLOOKUP(B15,'03_uFMEA'!$A:$R,11,FALSE))</f>
+        <v>4</v>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B15,'02_dFMEA'!$A:$S,13,FALSE),VLOOKUP(B15,'03_uFMEA'!$A:$R,12,FALSE))</f>
+        <v>❌</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="I15" s="21" t="e">
-        <f>VLOOKUP(B15,'02_dFMEA'!$A:$S,18,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J15" s="21" t="e">
-        <f>VLOOKUP(B15,'02_dFMEA'!$A:$S,19,FALSE)</f>
-        <v>#N/A</v>
+        <v>242</v>
+      </c>
+      <c r="I15" s="21">
+        <f>IFERROR(VLOOKUP(B15,'02_dFMEA'!$A:$S,18,FALSE),VLOOKUP(B15,'03_uFMEA'!$A:$R,17,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B15,'02_dFMEA'!$A:$S,19,FALSE),VLOOKUP(B15,'03_uFMEA'!$A:$R,18,FALSE))</f>
+        <v>✅</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5108,33 +5218,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B4" s="21">
         <f>COUNTA('04_Risk_Eval'!A4:A20)</f>
@@ -5147,7 +5257,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B5" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"❌*")</f>
@@ -5160,7 +5270,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"ALARP*")</f>
@@ -5173,7 +5283,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B7" s="21">
         <f>COUNTIF('04_Risk_Eval'!F4:F20,"✅*")</f>
@@ -5195,7 +5305,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5203,110 +5313,110 @@
     <col min="4" max="4" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5320,117 +5430,117 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>295</v>
-      </c>
       <c r="D9" s="22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
